--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5477"/>
+  <dimension ref="A1:B5484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55200,6 +55200,76 @@
         <v>1153650178.4</v>
       </c>
     </row>
+    <row r="5478">
+      <c r="A5478" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
+      <c r="B5478" t="n">
+        <v>1133849923.08</v>
+      </c>
+    </row>
+    <row r="5479">
+      <c r="A5479" t="inlineStr">
+        <is>
+          <t>2025-12-30</t>
+        </is>
+      </c>
+      <c r="B5479" t="n">
+        <v>931496430.58</v>
+      </c>
+    </row>
+    <row r="5480">
+      <c r="A5480" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="B5480" t="n">
+        <v>967038705.87</v>
+      </c>
+    </row>
+    <row r="5481">
+      <c r="A5481" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="B5481" t="n">
+        <v>1126647382.04</v>
+      </c>
+    </row>
+    <row r="5482">
+      <c r="A5482" t="inlineStr">
+        <is>
+          <t>2026-01-02</t>
+        </is>
+      </c>
+      <c r="B5482" t="n">
+        <v>1069660504.99</v>
+      </c>
+    </row>
+    <row r="5483">
+      <c r="A5483" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="B5483" t="n">
+        <v>1193315770.61</v>
+      </c>
+    </row>
+    <row r="5484">
+      <c r="A5484" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B5484" t="n">
+        <v>1066339234.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5484"/>
+  <dimension ref="A1:B5486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55270,6 +55270,26 @@
         <v>1066339234.68</v>
       </c>
     </row>
+    <row r="5485">
+      <c r="A5485" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="B5485" t="n">
+        <v>983330585.84</v>
+      </c>
+    </row>
+    <row r="5486">
+      <c r="A5486" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="B5486" t="n">
+        <v>976139083.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5486"/>
+  <dimension ref="A1:B5488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55290,6 +55290,26 @@
         <v>976139083.96</v>
       </c>
     </row>
+    <row r="5487">
+      <c r="A5487" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B5487" t="n">
+        <v>1077997873.64</v>
+      </c>
+    </row>
+    <row r="5488">
+      <c r="A5488" t="inlineStr">
+        <is>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="B5488" t="n">
+        <v>979226653.67</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5488"/>
+  <dimension ref="A1:B5491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55310,6 +55310,36 @@
         <v>979226653.67</v>
       </c>
     </row>
+    <row r="5489">
+      <c r="A5489" t="inlineStr">
+        <is>
+          <t>2026-01-09</t>
+        </is>
+      </c>
+      <c r="B5489" t="n">
+        <v>997885595.24</v>
+      </c>
+    </row>
+    <row r="5490">
+      <c r="A5490" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B5490" t="n">
+        <v>1170245543.23</v>
+      </c>
+    </row>
+    <row r="5491">
+      <c r="A5491" t="inlineStr">
+        <is>
+          <t>2026-01-11</t>
+        </is>
+      </c>
+      <c r="B5491" t="n">
+        <v>911167918.8099999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5491"/>
+  <dimension ref="A1:B5493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55340,6 +55340,26 @@
         <v>911167918.8099999</v>
       </c>
     </row>
+    <row r="5492">
+      <c r="A5492" t="inlineStr">
+        <is>
+          <t>2026-01-12</t>
+        </is>
+      </c>
+      <c r="B5492" t="n">
+        <v>1054917589.43</v>
+      </c>
+    </row>
+    <row r="5493">
+      <c r="A5493" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5493" t="n">
+        <v>967284693.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5493"/>
+  <dimension ref="A1:B5497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55360,6 +55360,46 @@
         <v>967284693.74</v>
       </c>
     </row>
+    <row r="5494">
+      <c r="A5494" t="inlineStr">
+        <is>
+          <t>2026-01-14</t>
+        </is>
+      </c>
+      <c r="B5494" t="n">
+        <v>911039633.0599999</v>
+      </c>
+    </row>
+    <row r="5495">
+      <c r="A5495" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="B5495" t="n">
+        <v>1002346208.66</v>
+      </c>
+    </row>
+    <row r="5496">
+      <c r="A5496" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B5496" t="n">
+        <v>928996031.3</v>
+      </c>
+    </row>
+    <row r="5497">
+      <c r="A5497" t="inlineStr">
+        <is>
+          <t>2026-01-17</t>
+        </is>
+      </c>
+      <c r="B5497" t="n">
+        <v>1107077539.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5497"/>
+  <dimension ref="A1:B5501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55400,6 +55400,46 @@
         <v>1107077539.65</v>
       </c>
     </row>
+    <row r="5498">
+      <c r="A5498" t="inlineStr">
+        <is>
+          <t>2026-01-18</t>
+        </is>
+      </c>
+      <c r="B5498" t="n">
+        <v>1033802143.04</v>
+      </c>
+    </row>
+    <row r="5499">
+      <c r="A5499" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B5499" t="n">
+        <v>1114267327.49</v>
+      </c>
+    </row>
+    <row r="5500">
+      <c r="A5500" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="B5500" t="n">
+        <v>1003756681.21</v>
+      </c>
+    </row>
+    <row r="5501">
+      <c r="A5501" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="B5501" t="n">
+        <v>977692676.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5501"/>
+  <dimension ref="A1:B5502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55440,6 +55440,16 @@
         <v>977692676.21</v>
       </c>
     </row>
+    <row r="5502">
+      <c r="A5502" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B5502" t="n">
+        <v>1157954020.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5502"/>
+  <dimension ref="A1:B5505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55450,6 +55450,36 @@
         <v>1157954020.62</v>
       </c>
     </row>
+    <row r="5503">
+      <c r="A5503" t="inlineStr">
+        <is>
+          <t>2026-01-23</t>
+        </is>
+      </c>
+      <c r="B5503" t="n">
+        <v>998399736.5</v>
+      </c>
+    </row>
+    <row r="5504">
+      <c r="A5504" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="B5504" t="n">
+        <v>762877748.0599999</v>
+      </c>
+    </row>
+    <row r="5505">
+      <c r="A5505" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B5505" t="n">
+        <v>727574056.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5505"/>
+  <dimension ref="A1:B5507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55480,6 +55480,26 @@
         <v>727574056.28</v>
       </c>
     </row>
+    <row r="5506">
+      <c r="A5506" t="inlineStr">
+        <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B5506" t="n">
+        <v>903573897.86</v>
+      </c>
+    </row>
+    <row r="5507">
+      <c r="A5507" t="inlineStr">
+        <is>
+          <t>2026-01-27</t>
+        </is>
+      </c>
+      <c r="B5507" t="n">
+        <v>876397180.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5507"/>
+  <dimension ref="A1:B5508"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55500,6 +55500,16 @@
         <v>876397180.11</v>
       </c>
     </row>
+    <row r="5508">
+      <c r="A5508" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B5508" t="n">
+        <v>805386065.85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5508"/>
+  <dimension ref="A1:B5509"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55510,6 +55510,16 @@
         <v>805386065.85</v>
       </c>
     </row>
+    <row r="5509">
+      <c r="A5509" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="B5509" t="n">
+        <v>932599208.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5509"/>
+  <dimension ref="A1:B5512"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55520,6 +55520,36 @@
         <v>932599208.91</v>
       </c>
     </row>
+    <row r="5510">
+      <c r="A5510" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="B5510" t="n">
+        <v>878655845.12</v>
+      </c>
+    </row>
+    <row r="5511">
+      <c r="A5511" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B5511" t="n">
+        <v>974481847.9400001</v>
+      </c>
+    </row>
+    <row r="5512">
+      <c r="A5512" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="B5512" t="n">
+        <v>889529658.33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5512"/>
+  <dimension ref="A1:B5514"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55550,6 +55550,26 @@
         <v>889529658.33</v>
       </c>
     </row>
+    <row r="5513">
+      <c r="A5513" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="B5513" t="n">
+        <v>880890756.49</v>
+      </c>
+    </row>
+    <row r="5514">
+      <c r="A5514" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B5514" t="n">
+        <v>913150822.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5514"/>
+  <dimension ref="A1:B5515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55570,6 +55570,16 @@
         <v>913150822.54</v>
       </c>
     </row>
+    <row r="5515">
+      <c r="A5515" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="B5515" t="n">
+        <v>1010536305.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5515"/>
+  <dimension ref="A1:B5516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55580,6 +55580,16 @@
         <v>1010536305.16</v>
       </c>
     </row>
+    <row r="5516">
+      <c r="A5516" t="inlineStr">
+        <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="B5516" t="n">
+        <v>911384150.8200001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5516"/>
+  <dimension ref="A1:B5520"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55590,6 +55590,46 @@
         <v>911384150.8200001</v>
       </c>
     </row>
+    <row r="5517">
+      <c r="A5517" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B5517" t="n">
+        <v>1037347550.77</v>
+      </c>
+    </row>
+    <row r="5518">
+      <c r="A5518" t="inlineStr">
+        <is>
+          <t>2026-02-07</t>
+        </is>
+      </c>
+      <c r="B5518" t="n">
+        <v>1167066970.44</v>
+      </c>
+    </row>
+    <row r="5519">
+      <c r="A5519" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="B5519" t="n">
+        <v>1062343256.12</v>
+      </c>
+    </row>
+    <row r="5520">
+      <c r="A5520" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B5520" t="n">
+        <v>1034503139.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5520"/>
+  <dimension ref="A1:B5521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55630,6 +55630,16 @@
         <v>1034503139.96</v>
       </c>
     </row>
+    <row r="5521">
+      <c r="A5521" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B5521" t="n">
+        <v>896732251.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5521"/>
+  <dimension ref="A1:B5526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55640,6 +55640,56 @@
         <v>896732251.8</v>
       </c>
     </row>
+    <row r="5522">
+      <c r="A5522" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B5522" t="n">
+        <v>975248703.71</v>
+      </c>
+    </row>
+    <row r="5523">
+      <c r="A5523" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B5523" t="n">
+        <v>1125469180.08</v>
+      </c>
+    </row>
+    <row r="5524">
+      <c r="A5524" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B5524" t="n">
+        <v>946344190.65</v>
+      </c>
+    </row>
+    <row r="5525">
+      <c r="A5525" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B5525" t="n">
+        <v>1018384704.07</v>
+      </c>
+    </row>
+    <row r="5526">
+      <c r="A5526" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B5526" t="n">
+        <v>1187535495.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5526"/>
+  <dimension ref="A1:B5527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55690,6 +55690,16 @@
         <v>1187535495.16</v>
       </c>
     </row>
+    <row r="5527">
+      <c r="A5527" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B5527" t="n">
+        <v>956366042.71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5527"/>
+  <dimension ref="A1:B5530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55693,11 +55693,41 @@
     <row r="5527">
       <c r="A5527" t="inlineStr">
         <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B5527" t="n">
+        <v>1110479011.01</v>
+      </c>
+    </row>
+    <row r="5528">
+      <c r="A5528" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="B5528" t="n">
+        <v>1033422526.86</v>
+      </c>
+    </row>
+    <row r="5529">
+      <c r="A5529" t="inlineStr">
+        <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="B5527" t="n">
+      <c r="B5529" t="n">
         <v>956366042.71</v>
+      </c>
+    </row>
+    <row r="5530">
+      <c r="A5530" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B5530" t="n">
+        <v>995626041.03</v>
       </c>
     </row>
   </sheetData>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5530"/>
+  <dimension ref="A1:B5533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55730,6 +55730,36 @@
         <v>995626041.03</v>
       </c>
     </row>
+    <row r="5531">
+      <c r="A5531" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B5531" t="n">
+        <v>988502175.83</v>
+      </c>
+    </row>
+    <row r="5532">
+      <c r="A5532" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B5532" t="n">
+        <v>891201625.37</v>
+      </c>
+    </row>
+    <row r="5533">
+      <c r="A5533" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B5533" t="n">
+        <v>1154389717.18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5533"/>
+  <dimension ref="A1:B5535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55760,6 +55760,26 @@
         <v>1154389717.18</v>
       </c>
     </row>
+    <row r="5534">
+      <c r="A5534" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B5534" t="n">
+        <v>1052331366.49</v>
+      </c>
+    </row>
+    <row r="5535">
+      <c r="A5535" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B5535" t="n">
+        <v>1170104239.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5535"/>
+  <dimension ref="A1:B5536"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55780,6 +55780,16 @@
         <v>1170104239.5</v>
       </c>
     </row>
+    <row r="5536">
+      <c r="A5536" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B5536" t="n">
+        <v>1174335385.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5536"/>
+  <dimension ref="A1:B5537"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55790,6 +55790,16 @@
         <v>1174335385.66</v>
       </c>
     </row>
+    <row r="5537">
+      <c r="A5537" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B5537" t="n">
+        <v>1001123285.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5537"/>
+  <dimension ref="A1:B5539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55800,6 +55800,26 @@
         <v>1001123285.8</v>
       </c>
     </row>
+    <row r="5538">
+      <c r="A5538" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B5538" t="n">
+        <v>1020816876.56</v>
+      </c>
+    </row>
+    <row r="5539">
+      <c r="A5539" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B5539" t="n">
+        <v>1023179310.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5539"/>
+  <dimension ref="A1:B5544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55820,6 +55820,56 @@
         <v>1023179310.07</v>
       </c>
     </row>
+    <row r="5540">
+      <c r="A5540" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B5540" t="n">
+        <v>1048255291.61</v>
+      </c>
+    </row>
+    <row r="5541">
+      <c r="A5541" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B5541" t="n">
+        <v>979998091.53</v>
+      </c>
+    </row>
+    <row r="5542">
+      <c r="A5542" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B5542" t="n">
+        <v>983408094.25</v>
+      </c>
+    </row>
+    <row r="5543">
+      <c r="A5543" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B5543" t="n">
+        <v>938633967.23</v>
+      </c>
+    </row>
+    <row r="5544">
+      <c r="A5544" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B5544" t="n">
+        <v>1212244696.72</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5544"/>
+  <dimension ref="A1:B5546"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55870,6 +55870,26 @@
         <v>1212244696.72</v>
       </c>
     </row>
+    <row r="5545">
+      <c r="A5545" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B5545" t="n">
+        <v>1049197242.39</v>
+      </c>
+    </row>
+    <row r="5546">
+      <c r="A5546" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B5546" t="n">
+        <v>946988896.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5546"/>
+  <dimension ref="A1:B5551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55890,6 +55890,56 @@
         <v>946988896.89</v>
       </c>
     </row>
+    <row r="5547">
+      <c r="A5547" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B5547" t="n">
+        <v>912113515.25</v>
+      </c>
+    </row>
+    <row r="5548">
+      <c r="A5548" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B5548" t="n">
+        <v>970323031.09</v>
+      </c>
+    </row>
+    <row r="5549">
+      <c r="A5549" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B5549" t="n">
+        <v>1005135848.7</v>
+      </c>
+    </row>
+    <row r="5550">
+      <c r="A5550" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B5550" t="n">
+        <v>969033781.17</v>
+      </c>
+    </row>
+    <row r="5551">
+      <c r="A5551" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B5551" t="n">
+        <v>929484045.76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5551"/>
+  <dimension ref="A1:B5555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55940,6 +55940,46 @@
         <v>929484045.76</v>
       </c>
     </row>
+    <row r="5552">
+      <c r="A5552" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B5552" t="n">
+        <v>875927511.39</v>
+      </c>
+    </row>
+    <row r="5553">
+      <c r="A5553" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B5553" t="n">
+        <v>906134044.02</v>
+      </c>
+    </row>
+    <row r="5554">
+      <c r="A5554" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B5554" t="n">
+        <v>926163705.88</v>
+      </c>
+    </row>
+    <row r="5555">
+      <c r="A5555" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B5555" t="n">
+        <v>900440293.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data_cripto/btc_hashrate.xlsx
+++ b/data_cripto/btc_hashrate.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5555"/>
+  <dimension ref="A1:B5560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55980,6 +55980,56 @@
         <v>900440293.34</v>
       </c>
     </row>
+    <row r="5556">
+      <c r="A5556" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B5556" t="n">
+        <v>870648176.5700001</v>
+      </c>
+    </row>
+    <row r="5557">
+      <c r="A5557" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B5557" t="n">
+        <v>1017494263.24</v>
+      </c>
+    </row>
+    <row r="5558">
+      <c r="A5558" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B5558" t="n">
+        <v>962927911.38</v>
+      </c>
+    </row>
+    <row r="5559">
+      <c r="A5559" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B5559" t="n">
+        <v>961633531.29</v>
+      </c>
+    </row>
+    <row r="5560">
+      <c r="A5560" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B5560" t="n">
+        <v>920251538.1900001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
